--- a/Datas/PlantData.xlsx
+++ b/Datas/PlantData.xlsx
@@ -13,6 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="PlantData" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PlantData!$A$3:$B$3</definedName>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
   <si>
     <t>int</t>
   </si>
@@ -69,7 +70,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>生长状态,0,2,0,1|结果,1,1,1,2</t>
+    <t>萌芽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小苗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大苗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成熟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>光杆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2|结果,3,1,0,3|成熟,4,1,0,4|光杆,5,1,0,5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -116,7 +141,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -124,6 +149,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -440,8 +468,10 @@
     <col min="5" max="5" width="15.375" style="1" customWidth="1"/>
     <col min="6" max="7" width="15" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="21.125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="7.75" style="1"/>
+    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
+    <col min="10" max="15" width="7.75" style="1"/>
+    <col min="16" max="16" width="22.625" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
@@ -502,7 +532,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" ht="81" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>8000</v>
       </c>
@@ -528,7 +558,7 @@
         <v>8000</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -541,4 +571,177 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I7"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="7" width="9" style="3"/>
+    <col min="8" max="8" width="38.5" style="3" customWidth="1"/>
+    <col min="9" max="9" width="33" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="str">
+        <f>B2&amp;","&amp;C2&amp;","&amp;D2&amp;","&amp;E2&amp;","&amp;F2</f>
+        <v>萌芽,0,1,0,0</v>
+      </c>
+      <c r="I2" s="3" t="str">
+        <f>I1&amp;"|"&amp;H2</f>
+        <v>|萌芽,0,1,0,0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="str">
+        <f>B3&amp;","&amp;C3&amp;","&amp;D3&amp;","&amp;E3&amp;","&amp;F3</f>
+        <v>小苗,1,1,0,1</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <f t="shared" ref="I3:I7" si="0">I2&amp;"|"&amp;H3</f>
+        <v>|萌芽,0,1,0,0|小苗,1,1,0,1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1" t="str">
+        <f>B4&amp;","&amp;C4&amp;","&amp;D4&amp;","&amp;E4&amp;","&amp;F4</f>
+        <v>大苗,2,1,0,2</v>
+      </c>
+      <c r="I4" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>|萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1" t="str">
+        <f>B5&amp;","&amp;C5&amp;","&amp;D5&amp;","&amp;E5&amp;","&amp;F5</f>
+        <v>结果,3,1,0,3</v>
+      </c>
+      <c r="I5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>|萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2|结果,3,1,0,3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>4</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1" t="str">
+        <f>B6&amp;","&amp;C6&amp;","&amp;D6&amp;","&amp;E6&amp;","&amp;F6</f>
+        <v>成熟,4,1,0,4</v>
+      </c>
+      <c r="I6" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>|萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2|结果,3,1,0,3|成熟,4,1,0,4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1" t="str">
+        <f>B7&amp;","&amp;C7&amp;","&amp;D7&amp;","&amp;E7&amp;","&amp;F7</f>
+        <v>光杆,5,1,0,5</v>
+      </c>
+      <c r="I7" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>|萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2|结果,3,1,0,3|成熟,4,1,0,4|光杆,5,1,0,5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Datas/PlantData.xlsx
+++ b/Datas/PlantData.xlsx
@@ -543,7 +543,7 @@
         <v>8000</v>
       </c>
       <c r="D4" s="1">
-        <v>1104</v>
+        <v>1004</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>
@@ -584,7 +584,7 @@
     <col min="10" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
@@ -602,7 +602,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="str">
-        <f>B2&amp;","&amp;C2&amp;","&amp;D2&amp;","&amp;E2&amp;","&amp;F2</f>
+        <f t="shared" ref="H2:H7" si="0">B2&amp;","&amp;C2&amp;","&amp;D2&amp;","&amp;E2&amp;","&amp;F2</f>
         <v>萌芽,0,1,0,0</v>
       </c>
       <c r="I2" s="3" t="str">
@@ -628,15 +628,15 @@
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="str">
-        <f>B3&amp;","&amp;C3&amp;","&amp;D3&amp;","&amp;E3&amp;","&amp;F3</f>
+        <f t="shared" si="0"/>
         <v>小苗,1,1,0,1</v>
       </c>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I7" si="0">I2&amp;"|"&amp;H3</f>
+        <f t="shared" ref="I3:I7" si="1">I2&amp;"|"&amp;H3</f>
         <v>|萌芽,0,1,0,0|小苗,1,1,0,1</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:9" ht="27" x14ac:dyDescent="0.15">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
@@ -654,15 +654,15 @@
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="str">
-        <f>B4&amp;","&amp;C4&amp;","&amp;D4&amp;","&amp;E4&amp;","&amp;F4</f>
+        <f t="shared" si="0"/>
         <v>大苗,2,1,0,2</v>
       </c>
       <c r="I4" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>|萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9" ht="27" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
@@ -680,15 +680,15 @@
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="str">
-        <f>B5&amp;","&amp;C5&amp;","&amp;D5&amp;","&amp;E5&amp;","&amp;F5</f>
+        <f t="shared" si="0"/>
         <v>结果,3,1,0,3</v>
       </c>
       <c r="I5" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>|萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2|结果,3,1,0,3</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
@@ -706,15 +706,15 @@
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="str">
-        <f>B6&amp;","&amp;C6&amp;","&amp;D6&amp;","&amp;E6&amp;","&amp;F6</f>
+        <f t="shared" si="0"/>
         <v>成熟,4,1,0,4</v>
       </c>
       <c r="I6" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>|萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2|结果,3,1,0,3|成熟,4,1,0,4</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
@@ -732,11 +732,11 @@
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="str">
-        <f>B7&amp;","&amp;C7&amp;","&amp;D7&amp;","&amp;E7&amp;","&amp;F7</f>
+        <f t="shared" si="0"/>
         <v>光杆,5,1,0,5</v>
       </c>
       <c r="I7" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>|萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2|结果,3,1,0,3|成熟,4,1,0,4|光杆,5,1,0,5</v>
       </c>
     </row>

--- a/Datas/PlantData.xlsx
+++ b/Datas/PlantData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="50">
   <si>
     <t>int</t>
   </si>
@@ -66,10 +66,6 @@
     <t>GrowthStageStr</t>
   </si>
   <si>
-    <t>玉米</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>萌芽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -95,6 +91,106 @@
   </si>
   <si>
     <t>萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2|结果,3,1,0,3|成熟,4,1,0,4|光杆,5,1,0,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>芜菁</t>
+  </si>
+  <si>
+    <t>菠萝</t>
+  </si>
+  <si>
+    <t>大麦</t>
+  </si>
+  <si>
+    <t>草莓</t>
+  </si>
+  <si>
+    <t>西兰花</t>
+  </si>
+  <si>
+    <t>西瓜</t>
+  </si>
+  <si>
+    <t>玉米</t>
+  </si>
+  <si>
+    <t>蓝莓</t>
+  </si>
+  <si>
+    <t>大葱</t>
+  </si>
+  <si>
+    <t>葡萄</t>
+  </si>
+  <si>
+    <t>豌豆</t>
+  </si>
+  <si>
+    <t>土豆</t>
+  </si>
+  <si>
+    <t>紫甘蓝</t>
+  </si>
+  <si>
+    <t>番茄</t>
+  </si>
+  <si>
+    <t>茄子</t>
+  </si>
+  <si>
+    <t>大蒜</t>
+  </si>
+  <si>
+    <t>卷心菜</t>
+  </si>
+  <si>
+    <t>啤酒花</t>
+  </si>
+  <si>
+    <t>奇异果</t>
+  </si>
+  <si>
+    <t>甜菜</t>
+  </si>
+  <si>
+    <t>萝卜</t>
+  </si>
+  <si>
+    <t>咖啡</t>
+  </si>
+  <si>
+    <t>南瓜</t>
+  </si>
+  <si>
+    <t>芦笋</t>
+  </si>
+  <si>
+    <t>黄瓜</t>
+  </si>
+  <si>
+    <t>胡萝卜</t>
+  </si>
+  <si>
+    <t>辣椒</t>
+  </si>
+  <si>
+    <t>红薯</t>
+  </si>
+  <si>
+    <t>春</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>秋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冬</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -119,12 +215,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -141,7 +243,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -153,6 +255,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -459,7 +567,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:I4"/>
+  <dimension ref="A2:I31"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -534,31 +642,814 @@
     </row>
     <row r="4" spans="1:9" ht="81" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
-        <v>8000</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1">
-        <v>8000</v>
+        <v>8001</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1101</v>
       </c>
       <c r="D4" s="1">
+        <v>1001</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
+        <v>8001</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A5" s="1">
+        <v>8002</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1102</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1002</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
+        <v>8002</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A6" s="1">
+        <v>8003</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1103</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1003</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>8003</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A7" s="1">
+        <v>8004</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1104</v>
+      </c>
+      <c r="D7" s="1">
         <v>1004</v>
       </c>
-      <c r="E4" s="1">
-        <v>2</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1">
-        <v>8000</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>18</v>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
+        <v>8004</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A8" s="1">
+        <v>8005</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1105</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1005</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>8005</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A9" s="1">
+        <v>8006</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1106</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1006</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
+        <v>8006</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A10" s="1">
+        <v>8007</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1107</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1007</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1">
+        <v>8007</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A11" s="1">
+        <v>8008</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1108</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1008</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
+        <v>8008</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A12" s="1">
+        <v>8009</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1109</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1009</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
+        <v>8009</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A13" s="1">
+        <v>8010</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1110</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1010</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1">
+        <v>8010</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A14" s="1">
+        <v>8011</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1111</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1011</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>8011</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A15" s="1">
+        <v>8012</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1112</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1012</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
+        <v>8012</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A16" s="1">
+        <v>8013</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1113</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1013</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1">
+        <v>8013</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A17" s="1">
+        <v>8014</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1114</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1014</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
+        <v>8014</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A18" s="1">
+        <v>8015</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1115</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1015</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
+        <v>8015</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A19" s="1">
+        <v>8016</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="5">
+        <v>1116</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1016</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1">
+        <v>8016</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A20" s="1">
+        <v>8017</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="5">
+        <v>1117</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1017</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1">
+        <v>8017</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A21" s="1">
+        <v>8018</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1118</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1018</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>8018</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A22" s="1">
+        <v>8019</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1119</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1019</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
+        <v>8019</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A23" s="1">
+        <v>8020</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1120</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1020</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1">
+        <v>8020</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A24" s="1">
+        <v>8021</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="5">
+        <v>1121</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1021</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
+        <v>8021</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A25" s="1">
+        <v>8022</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="5">
+        <v>1122</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1022</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1">
+        <v>8022</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A26" s="1">
+        <v>8023</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="5">
+        <v>1123</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1023</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1">
+        <v>8023</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A27" s="1">
+        <v>8024</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="5">
+        <v>1124</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1024</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
+        <v>8024</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A28" s="1">
+        <v>8025</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="5">
+        <v>1125</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1025</v>
+      </c>
+      <c r="E28" s="1">
+        <v>2</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1">
+        <v>8025</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A29" s="1">
+        <v>8026</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="5">
+        <v>1126</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1026</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1">
+        <v>8026</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A30" s="1">
+        <v>8027</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="5">
+        <v>1127</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1027</v>
+      </c>
+      <c r="E30" s="1">
+        <v>2</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1">
+        <v>8027</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A31" s="1">
+        <v>8028</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="5">
+        <v>1128</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1028</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1">
+        <v>8028</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -575,18 +1466,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I7"/>
+  <dimension ref="A2:R35"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="7" width="9" style="3"/>
-    <col min="8" max="8" width="38.5" style="3" customWidth="1"/>
-    <col min="9" max="9" width="33" style="3" customWidth="1"/>
+    <col min="8" max="9" width="8" style="3" customWidth="1"/>
     <col min="10" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>0</v>
@@ -610,9 +1500,9 @@
         <v>|萌芽,0,1,0,0</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -636,9 +1526,9 @@
         <v>|萌芽,0,1,0,0|小苗,1,1,0,1</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:17" ht="27" x14ac:dyDescent="0.15">
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
@@ -662,9 +1552,9 @@
         <v>|萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:17" ht="27" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1">
         <v>3</v>
@@ -688,9 +1578,9 @@
         <v>|萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2|结果,3,1,0,3</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:17" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
@@ -714,9 +1604,9 @@
         <v>|萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2|结果,3,1,0,3|成熟,4,1,0,4</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:17" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1">
         <v>5</v>
@@ -740,8 +1630,331 @@
         <v>|萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2|结果,3,1,0,3|成熟,4,1,0,4|光杆,5,1,0,5</v>
       </c>
     </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="H13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="H14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="H15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="H16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="H18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A19" s="3">
+        <v>1</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A20" s="3">
+        <v>2</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A21" s="3">
+        <v>3</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A22" s="3">
+        <v>4</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A23" s="3">
+        <v>5</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A24" s="3">
+        <v>6</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A25" s="3">
+        <v>7</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A26" s="3">
+        <v>8</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A27" s="3">
+        <v>9</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A28" s="3">
+        <v>10</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A29" s="3">
+        <v>11</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A30" s="3">
+        <v>12</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A31" s="3">
+        <v>13</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A32" s="3">
+        <v>14</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="3:6" x14ac:dyDescent="0.15">
+      <c r="C33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="3:6" x14ac:dyDescent="0.15">
+      <c r="C34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6" x14ac:dyDescent="0.15">
+      <c r="C35" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Datas/PlantData.xlsx
+++ b/Datas/PlantData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="51">
   <si>
     <t>int</t>
   </si>
@@ -191,6 +191,10 @@
   </si>
   <si>
     <t>冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小麦</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1196,7 +1200,7 @@
         <v>8020</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C23" s="5">
         <v>1120</v>
@@ -1474,7 +1478,7 @@
     <col min="10" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:17" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1500,7 +1504,7 @@
         <v>|萌芽,0,1,0,0</v>
       </c>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:17" ht="67.5" x14ac:dyDescent="0.15">
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1526,7 +1530,7 @@
         <v>|萌芽,0,1,0,0|小苗,1,1,0,1</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="27" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:17" ht="94.5" x14ac:dyDescent="0.15">
       <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
@@ -1552,7 +1556,7 @@
         <v>|萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="27" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:17" ht="121.5" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1578,7 +1582,7 @@
         <v>|萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2|结果,3,1,0,3</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:17" ht="148.5" x14ac:dyDescent="0.15">
       <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1604,7 +1608,7 @@
         <v>|萌芽,0,1,0,0|小苗,1,1,0,1|大苗,2,1,0,2|结果,3,1,0,3|成熟,4,1,0,4</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:17" ht="175.5" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>16</v>
       </c>

--- a/Datas/PlantData.xlsx
+++ b/Datas/PlantData.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="88">
   <si>
     <t>int</t>
   </si>
@@ -288,6 +288,33 @@
   </si>
   <si>
     <t>萌芽,54,0|小苗,54,0|大苗,54,1|结果,54,2|成熟,54,2|光杆,0,0</t>
+  </si>
+  <si>
+    <t>plantIcon</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list&lt;int&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goodSeason</t>
+  </si>
+  <si>
+    <t>badSeason</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>openLevel</t>
+  </si>
+  <si>
+    <t>芜菁_04</t>
   </si>
 </sst>
 </file>
@@ -675,22 +702,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:I31"/>
+  <dimension ref="A2:M31"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="4" customWidth="1"/>
     <col min="2" max="2" width="13" style="4" customWidth="1"/>
     <col min="3" max="4" width="7.75" style="4"/>
-    <col min="5" max="5" width="15.375" style="4" customWidth="1"/>
-    <col min="6" max="7" width="15" style="4" customWidth="1"/>
-    <col min="8" max="8" width="9" style="4" customWidth="1"/>
-    <col min="9" max="9" width="69.5" style="5" customWidth="1"/>
-    <col min="10" max="15" width="7.75" style="4"/>
-    <col min="16" max="16" width="22.625" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="7.75" style="4"/>
+    <col min="5" max="5" width="19.75" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.875" style="4" customWidth="1"/>
+    <col min="7" max="8" width="15.875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="15.375" style="4" customWidth="1"/>
+    <col min="10" max="11" width="15" style="4" customWidth="1"/>
+    <col min="12" max="12" width="9" style="4" customWidth="1"/>
+    <col min="13" max="13" width="69.5" style="5" customWidth="1"/>
+    <col min="14" max="19" width="7.75" style="4"/>
+    <col min="20" max="20" width="22.625" style="4" customWidth="1"/>
+    <col min="21" max="16384" width="7.75" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -704,22 +734,34 @@
         <v>0</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+        <v>85</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -733,22 +775,34 @@
         <v>5</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A4" s="4">
         <v>8001</v>
       </c>
@@ -761,8 +815,8 @@
       <c r="D4" s="4">
         <v>1001</v>
       </c>
-      <c r="E4" s="4">
-        <v>3</v>
+      <c r="E4" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="F4" s="4">
         <v>1</v>
@@ -771,13 +825,25 @@
         <v>3</v>
       </c>
       <c r="H4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4">
+        <v>3</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1</v>
+      </c>
+      <c r="K4" s="4">
+        <v>3</v>
+      </c>
+      <c r="L4" s="4">
         <v>8001</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="M4" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A5" s="4">
         <v>8002</v>
       </c>
@@ -790,8 +856,9 @@
       <c r="D5" s="4">
         <v>1002</v>
       </c>
-      <c r="E5" s="4">
-        <v>3</v>
+      <c r="E5" s="4" t="str">
+        <f>B5&amp;"_04"</f>
+        <v>卷心菜_04</v>
       </c>
       <c r="F5" s="4">
         <v>1</v>
@@ -800,13 +867,25 @@
         <v>3</v>
       </c>
       <c r="H5" s="4">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4">
+        <v>3</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4">
+        <v>3</v>
+      </c>
+      <c r="L5" s="4">
         <v>8002</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6" s="4">
         <v>8003</v>
       </c>
@@ -819,23 +898,36 @@
       <c r="D6" s="4">
         <v>1003</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="4" t="str">
+        <f>B6&amp;"_04"</f>
+        <v>大葱_04</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4">
+        <v>3</v>
+      </c>
+      <c r="H6" s="4">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4">
         <v>4</v>
       </c>
-      <c r="F6" s="4">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4">
-        <v>3</v>
-      </c>
-      <c r="H6" s="4">
+      <c r="J6" s="4">
+        <v>1</v>
+      </c>
+      <c r="K6" s="4">
+        <v>3</v>
+      </c>
+      <c r="L6" s="4">
         <v>8003</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="M6" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A7" s="4">
         <v>8004</v>
       </c>
@@ -848,23 +940,36 @@
       <c r="D7" s="4">
         <v>1004</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="4" t="str">
+        <f>B7&amp;"_04"</f>
+        <v>萝卜_04</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4">
+        <v>3</v>
+      </c>
+      <c r="H7" s="4">
+        <v>2</v>
+      </c>
+      <c r="I7" s="4">
         <v>4</v>
       </c>
-      <c r="F7" s="4">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4">
-        <v>3</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="J7" s="4">
+        <v>1</v>
+      </c>
+      <c r="K7" s="4">
+        <v>3</v>
+      </c>
+      <c r="L7" s="4">
         <v>8004</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="M7" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A8" s="4">
         <v>8005</v>
       </c>
@@ -877,8 +982,9 @@
       <c r="D8" s="4">
         <v>1005</v>
       </c>
-      <c r="E8" s="4">
-        <v>3</v>
+      <c r="E8" s="4" t="str">
+        <f>B8&amp;"_04"</f>
+        <v>紫甘蓝_04</v>
       </c>
       <c r="F8" s="4">
         <v>1</v>
@@ -887,13 +993,25 @@
         <v>3</v>
       </c>
       <c r="H8" s="4">
+        <v>2</v>
+      </c>
+      <c r="I8" s="4">
+        <v>3</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1</v>
+      </c>
+      <c r="K8" s="4">
+        <v>3</v>
+      </c>
+      <c r="L8" s="4">
         <v>8005</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="M8" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A9" s="4">
         <v>8006</v>
       </c>
@@ -906,23 +1024,36 @@
       <c r="D9" s="4">
         <v>1006</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="4" t="str">
+        <f>B9&amp;"_04"</f>
+        <v>黄瓜_04</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4">
+        <v>3</v>
+      </c>
+      <c r="H9" s="4">
+        <v>2</v>
+      </c>
+      <c r="I9" s="4">
         <v>4</v>
       </c>
-      <c r="F9" s="4">
-        <v>3</v>
-      </c>
-      <c r="G9" s="4">
-        <v>3</v>
-      </c>
-      <c r="H9" s="4">
+      <c r="J9" s="4">
+        <v>3</v>
+      </c>
+      <c r="K9" s="4">
+        <v>3</v>
+      </c>
+      <c r="L9" s="4">
         <v>8006</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="M9" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A10" s="4">
         <v>8007</v>
       </c>
@@ -935,8 +1066,9 @@
       <c r="D10" s="4">
         <v>1007</v>
       </c>
-      <c r="E10" s="4">
-        <v>3</v>
+      <c r="E10" s="4" t="str">
+        <f>B10&amp;"_04"</f>
+        <v>西兰花_04</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
@@ -945,13 +1077,25 @@
         <v>3</v>
       </c>
       <c r="H10" s="4">
+        <v>3</v>
+      </c>
+      <c r="I10" s="4">
+        <v>3</v>
+      </c>
+      <c r="J10" s="4">
+        <v>1</v>
+      </c>
+      <c r="K10" s="4">
+        <v>3</v>
+      </c>
+      <c r="L10" s="4">
         <v>8007</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="M10" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A11" s="4">
         <v>8008</v>
       </c>
@@ -964,23 +1108,36 @@
       <c r="D11" s="4">
         <v>1008</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="4" t="str">
+        <f>B11&amp;"_04"</f>
+        <v>番茄_04</v>
+      </c>
+      <c r="F11" s="4">
+        <v>2</v>
+      </c>
+      <c r="G11" s="4">
         <v>4</v>
       </c>
-      <c r="F11" s="4">
-        <v>2</v>
-      </c>
-      <c r="G11" s="4">
-        <v>3</v>
-      </c>
       <c r="H11" s="4">
+        <v>3</v>
+      </c>
+      <c r="I11" s="4">
+        <v>4</v>
+      </c>
+      <c r="J11" s="4">
+        <v>2</v>
+      </c>
+      <c r="K11" s="4">
+        <v>3</v>
+      </c>
+      <c r="L11" s="4">
         <v>8008</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="M11" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A12" s="4">
         <v>8009</v>
       </c>
@@ -993,23 +1150,36 @@
       <c r="D12" s="4">
         <v>1009</v>
       </c>
-      <c r="E12" s="4">
-        <v>3</v>
+      <c r="E12" s="4" t="str">
+        <f>B12&amp;"_04"</f>
+        <v>胡萝卜_04</v>
       </c>
       <c r="F12" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" s="4">
+        <v>3</v>
+      </c>
+      <c r="I12" s="4">
+        <v>3</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1</v>
+      </c>
+      <c r="K12" s="4">
+        <v>3</v>
+      </c>
+      <c r="L12" s="4">
         <v>8009</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="M12" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A13" s="4">
         <v>8010</v>
       </c>
@@ -1022,23 +1192,36 @@
       <c r="D13" s="4">
         <v>1010</v>
       </c>
-      <c r="E13" s="4">
-        <v>2</v>
+      <c r="E13" s="4" t="str">
+        <f>B13&amp;"_04"</f>
+        <v>西瓜_04</v>
       </c>
       <c r="F13" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" s="4">
+        <v>4</v>
+      </c>
+      <c r="I13" s="4">
+        <v>2</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1</v>
+      </c>
+      <c r="K13" s="4">
+        <v>3</v>
+      </c>
+      <c r="L13" s="4">
         <v>8010</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="M13" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A14" s="4">
         <v>8011</v>
       </c>
@@ -1051,23 +1234,36 @@
       <c r="D14" s="4">
         <v>1011</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="4" t="str">
+        <f>B14&amp;"_04"</f>
+        <v>辣椒_04</v>
+      </c>
+      <c r="F14" s="4">
+        <v>3</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4">
+        <v>4</v>
+      </c>
+      <c r="I14" s="4">
         <v>5</v>
       </c>
-      <c r="F14" s="4">
-        <v>3</v>
-      </c>
-      <c r="G14" s="4">
-        <v>3</v>
-      </c>
-      <c r="H14" s="4">
+      <c r="J14" s="4">
+        <v>3</v>
+      </c>
+      <c r="K14" s="4">
+        <v>3</v>
+      </c>
+      <c r="L14" s="4">
         <v>8011</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="M14" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A15" s="4">
         <v>8012</v>
       </c>
@@ -1080,23 +1276,36 @@
       <c r="D15" s="4">
         <v>1012</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="4" t="str">
+        <f>B15&amp;"_04"</f>
+        <v>奇异果_04</v>
+      </c>
+      <c r="F15" s="4">
+        <v>3</v>
+      </c>
+      <c r="G15" s="4">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4">
+        <v>4</v>
+      </c>
+      <c r="I15" s="4">
         <v>6</v>
       </c>
-      <c r="F15" s="4">
-        <v>2</v>
-      </c>
-      <c r="G15" s="4">
-        <v>3</v>
-      </c>
-      <c r="H15" s="4">
+      <c r="J15" s="4">
+        <v>2</v>
+      </c>
+      <c r="K15" s="4">
+        <v>3</v>
+      </c>
+      <c r="L15" s="4">
         <v>8012</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="M15" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A16" s="4">
         <v>8013</v>
       </c>
@@ -1109,23 +1318,36 @@
       <c r="D16" s="4">
         <v>1013</v>
       </c>
-      <c r="E16" s="4">
-        <v>3</v>
+      <c r="E16" s="4" t="str">
+        <f>B16&amp;"_04"</f>
+        <v>茄子_04</v>
       </c>
       <c r="F16" s="4">
+        <v>3</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4">
+        <v>5</v>
+      </c>
+      <c r="I16" s="4">
+        <v>3</v>
+      </c>
+      <c r="J16" s="4">
         <v>4</v>
       </c>
-      <c r="G16" s="4">
-        <v>3</v>
-      </c>
-      <c r="H16" s="4">
+      <c r="K16" s="4">
+        <v>3</v>
+      </c>
+      <c r="L16" s="4">
         <v>8013</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="M16" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A17" s="4">
         <v>8014</v>
       </c>
@@ -1138,23 +1360,36 @@
       <c r="D17" s="4">
         <v>1014</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="4" t="str">
+        <f>B17&amp;"_04"</f>
+        <v>豌豆_04</v>
+      </c>
+      <c r="F17" s="4">
+        <v>3</v>
+      </c>
+      <c r="G17" s="4">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4">
+        <v>5</v>
+      </c>
+      <c r="I17" s="4">
         <v>6</v>
       </c>
-      <c r="F17" s="4">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4">
-        <v>3</v>
-      </c>
-      <c r="H17" s="4">
+      <c r="J17" s="4">
+        <v>1</v>
+      </c>
+      <c r="K17" s="4">
+        <v>3</v>
+      </c>
+      <c r="L17" s="4">
         <v>8014</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="M17" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A18" s="4">
         <v>8015</v>
       </c>
@@ -1167,23 +1402,36 @@
       <c r="D18" s="4">
         <v>1015</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="4" t="str">
+        <f>B18&amp;"_04"</f>
+        <v>土豆_04</v>
+      </c>
+      <c r="F18" s="4">
         <v>4</v>
       </c>
-      <c r="F18" s="4">
-        <v>1</v>
-      </c>
       <c r="G18" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="4">
+        <v>5</v>
+      </c>
+      <c r="I18" s="4">
+        <v>4</v>
+      </c>
+      <c r="J18" s="4">
+        <v>1</v>
+      </c>
+      <c r="K18" s="4">
+        <v>3</v>
+      </c>
+      <c r="L18" s="4">
         <v>8015</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="M18" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A19" s="4">
         <v>8016</v>
       </c>
@@ -1196,23 +1444,36 @@
       <c r="D19" s="4">
         <v>1016</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="4" t="str">
+        <f>B19&amp;"_04"</f>
+        <v>大蒜_04</v>
+      </c>
+      <c r="F19" s="4">
+        <v>4</v>
+      </c>
+      <c r="G19" s="4">
+        <v>2</v>
+      </c>
+      <c r="H19" s="4">
         <v>6</v>
       </c>
-      <c r="F19" s="4">
-        <v>1</v>
-      </c>
-      <c r="G19" s="4">
-        <v>3</v>
-      </c>
-      <c r="H19" s="4">
+      <c r="I19" s="4">
+        <v>6</v>
+      </c>
+      <c r="J19" s="4">
+        <v>1</v>
+      </c>
+      <c r="K19" s="4">
+        <v>3</v>
+      </c>
+      <c r="L19" s="4">
         <v>8016</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="M19" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A20" s="4">
         <v>8017</v>
       </c>
@@ -1225,23 +1486,36 @@
       <c r="D20" s="4">
         <v>1017</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="4" t="str">
+        <f>B20&amp;"_04"</f>
+        <v>芦笋_04</v>
+      </c>
+      <c r="F20" s="4">
         <v>4</v>
       </c>
-      <c r="F20" s="4">
-        <v>1</v>
-      </c>
       <c r="G20" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="4">
+        <v>6</v>
+      </c>
+      <c r="I20" s="4">
+        <v>4</v>
+      </c>
+      <c r="J20" s="4">
+        <v>1</v>
+      </c>
+      <c r="K20" s="4">
+        <v>3</v>
+      </c>
+      <c r="L20" s="4">
         <v>8017</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="M20" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A21" s="4">
         <v>8018</v>
       </c>
@@ -1254,23 +1528,36 @@
       <c r="D21" s="4">
         <v>1018</v>
       </c>
-      <c r="E21" s="4">
-        <v>3</v>
+      <c r="E21" s="4" t="str">
+        <f>B21&amp;"_04"</f>
+        <v>南瓜_04</v>
       </c>
       <c r="F21" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" s="4">
+        <v>6</v>
+      </c>
+      <c r="I21" s="4">
+        <v>3</v>
+      </c>
+      <c r="J21" s="4">
+        <v>2</v>
+      </c>
+      <c r="K21" s="4">
+        <v>3</v>
+      </c>
+      <c r="L21" s="4">
         <v>8018</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="M21" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A22" s="4">
         <v>8019</v>
       </c>
@@ -1283,23 +1570,36 @@
       <c r="D22" s="4">
         <v>1019</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="4" t="str">
+        <f>B22&amp;"_04"</f>
+        <v>玉米_04</v>
+      </c>
+      <c r="F22" s="4">
+        <v>3</v>
+      </c>
+      <c r="G22" s="4">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4">
+        <v>7</v>
+      </c>
+      <c r="I22" s="4">
         <v>8</v>
       </c>
-      <c r="F22" s="4">
-        <v>1</v>
-      </c>
-      <c r="G22" s="4">
-        <v>3</v>
-      </c>
-      <c r="H22" s="4">
+      <c r="J22" s="4">
+        <v>1</v>
+      </c>
+      <c r="K22" s="4">
+        <v>3</v>
+      </c>
+      <c r="L22" s="4">
         <v>8019</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="M22" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A23" s="4">
         <v>8020</v>
       </c>
@@ -1312,23 +1612,36 @@
       <c r="D23" s="4">
         <v>1020</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="4" t="str">
+        <f>B23&amp;"_04"</f>
+        <v>小麦_04</v>
+      </c>
+      <c r="F23" s="4">
+        <v>3</v>
+      </c>
+      <c r="G23" s="4">
+        <v>1</v>
+      </c>
+      <c r="H23" s="4">
+        <v>7</v>
+      </c>
+      <c r="I23" s="4">
         <v>8</v>
       </c>
-      <c r="F23" s="4">
-        <v>1</v>
-      </c>
-      <c r="G23" s="4">
-        <v>3</v>
-      </c>
-      <c r="H23" s="4">
+      <c r="J23" s="4">
+        <v>1</v>
+      </c>
+      <c r="K23" s="4">
+        <v>3</v>
+      </c>
+      <c r="L23" s="4">
         <v>8020</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="M23" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A24" s="4">
         <v>8021</v>
       </c>
@@ -1341,23 +1654,36 @@
       <c r="D24" s="4">
         <v>1021</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="4" t="str">
+        <f>B24&amp;"_04"</f>
+        <v>啤酒花_04</v>
+      </c>
+      <c r="F24" s="4">
+        <v>2</v>
+      </c>
+      <c r="G24" s="4">
+        <v>4</v>
+      </c>
+      <c r="H24" s="4">
+        <v>7</v>
+      </c>
+      <c r="I24" s="4">
         <v>8</v>
       </c>
-      <c r="F24" s="4">
+      <c r="J24" s="4">
         <v>4</v>
       </c>
-      <c r="G24" s="4">
-        <v>3</v>
-      </c>
-      <c r="H24" s="4">
+      <c r="K24" s="4">
+        <v>3</v>
+      </c>
+      <c r="L24" s="4">
         <v>8021</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="M24" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A25" s="4">
         <v>8022</v>
       </c>
@@ -1370,23 +1696,36 @@
       <c r="D25" s="4">
         <v>1022</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="4" t="str">
+        <f>B25&amp;"_04"</f>
+        <v>葡萄_04</v>
+      </c>
+      <c r="F25" s="4">
+        <v>2</v>
+      </c>
+      <c r="G25" s="4">
+        <v>4</v>
+      </c>
+      <c r="H25" s="4">
         <v>8</v>
       </c>
-      <c r="F25" s="4">
+      <c r="I25" s="4">
+        <v>8</v>
+      </c>
+      <c r="J25" s="4">
         <v>6</v>
       </c>
-      <c r="G25" s="4">
-        <v>3</v>
-      </c>
-      <c r="H25" s="4">
+      <c r="K25" s="4">
+        <v>3</v>
+      </c>
+      <c r="L25" s="4">
         <v>8022</v>
       </c>
-      <c r="I25" s="5" t="s">
+      <c r="M25" s="5" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A26" s="4">
         <v>8023</v>
       </c>
@@ -1399,23 +1738,36 @@
       <c r="D26" s="4">
         <v>1023</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="4" t="str">
+        <f>B26&amp;"_04"</f>
+        <v>菠萝_04</v>
+      </c>
+      <c r="F26" s="4">
+        <v>2</v>
+      </c>
+      <c r="G26" s="4">
         <v>4</v>
       </c>
-      <c r="F26" s="4">
+      <c r="H26" s="4">
+        <v>8</v>
+      </c>
+      <c r="I26" s="4">
+        <v>4</v>
+      </c>
+      <c r="J26" s="4">
         <v>6</v>
       </c>
-      <c r="G26" s="4">
-        <v>3</v>
-      </c>
-      <c r="H26" s="4">
+      <c r="K26" s="4">
+        <v>3</v>
+      </c>
+      <c r="L26" s="4">
         <v>8023</v>
       </c>
-      <c r="I26" s="5" t="s">
+      <c r="M26" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A27" s="4">
         <v>8024</v>
       </c>
@@ -1428,23 +1780,36 @@
       <c r="D27" s="4">
         <v>1024</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="4" t="str">
+        <f>B27&amp;"_04"</f>
+        <v>咖啡_04</v>
+      </c>
+      <c r="F27" s="4">
+        <v>2</v>
+      </c>
+      <c r="G27" s="4">
+        <v>4</v>
+      </c>
+      <c r="H27" s="4">
+        <v>8</v>
+      </c>
+      <c r="I27" s="4">
         <v>6</v>
       </c>
-      <c r="F27" s="4">
+      <c r="J27" s="4">
         <v>4</v>
       </c>
-      <c r="G27" s="4">
-        <v>3</v>
-      </c>
-      <c r="H27" s="4">
+      <c r="K27" s="4">
+        <v>3</v>
+      </c>
+      <c r="L27" s="4">
         <v>8024</v>
       </c>
-      <c r="I27" s="5" t="s">
+      <c r="M27" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A28" s="4">
         <v>8025</v>
       </c>
@@ -1457,23 +1822,36 @@
       <c r="D28" s="4">
         <v>1025</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="4" t="str">
+        <f>B28&amp;"_04"</f>
+        <v>草莓_04</v>
+      </c>
+      <c r="F28" s="4">
+        <v>4</v>
+      </c>
+      <c r="G28" s="4">
+        <v>2</v>
+      </c>
+      <c r="H28" s="4">
+        <v>9</v>
+      </c>
+      <c r="I28" s="4">
         <v>6</v>
       </c>
-      <c r="F28" s="4">
-        <v>2</v>
-      </c>
-      <c r="G28" s="4">
-        <v>3</v>
-      </c>
-      <c r="H28" s="4">
+      <c r="J28" s="4">
+        <v>2</v>
+      </c>
+      <c r="K28" s="4">
+        <v>3</v>
+      </c>
+      <c r="L28" s="4">
         <v>8025</v>
       </c>
-      <c r="I28" s="5" t="s">
+      <c r="M28" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A29" s="4">
         <v>8026</v>
       </c>
@@ -1486,23 +1864,36 @@
       <c r="D29" s="4">
         <v>1026</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="4" t="str">
+        <f>B29&amp;"_04"</f>
+        <v>蓝莓_04</v>
+      </c>
+      <c r="F29" s="4">
+        <v>4</v>
+      </c>
+      <c r="G29" s="4">
+        <v>2</v>
+      </c>
+      <c r="H29" s="4">
+        <v>9</v>
+      </c>
+      <c r="I29" s="4">
         <v>6</v>
       </c>
-      <c r="F29" s="4">
-        <v>2</v>
-      </c>
-      <c r="G29" s="4">
-        <v>3</v>
-      </c>
-      <c r="H29" s="4">
+      <c r="J29" s="4">
+        <v>2</v>
+      </c>
+      <c r="K29" s="4">
+        <v>3</v>
+      </c>
+      <c r="L29" s="4">
         <v>8026</v>
       </c>
-      <c r="I29" s="5" t="s">
+      <c r="M29" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A30" s="4">
         <v>8027</v>
       </c>
@@ -1515,23 +1906,36 @@
       <c r="D30" s="4">
         <v>1027</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="4" t="str">
+        <f>B30&amp;"_04"</f>
+        <v>红薯_04</v>
+      </c>
+      <c r="F30" s="4">
+        <v>4</v>
+      </c>
+      <c r="G30" s="4">
+        <v>2</v>
+      </c>
+      <c r="H30" s="4">
+        <v>9</v>
+      </c>
+      <c r="I30" s="4">
         <v>6</v>
       </c>
-      <c r="F30" s="4">
-        <v>1</v>
-      </c>
-      <c r="G30" s="4">
-        <v>3</v>
-      </c>
-      <c r="H30" s="4">
+      <c r="J30" s="4">
+        <v>1</v>
+      </c>
+      <c r="K30" s="4">
+        <v>3</v>
+      </c>
+      <c r="L30" s="4">
         <v>8027</v>
       </c>
-      <c r="I30" s="5" t="s">
+      <c r="M30" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A31" s="4">
         <v>8028</v>
       </c>
@@ -1544,19 +1948,32 @@
       <c r="D31" s="4">
         <v>1028</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="4" t="str">
+        <f>B31&amp;"_04"</f>
+        <v>甜菜_04</v>
+      </c>
+      <c r="F31" s="4">
+        <v>4</v>
+      </c>
+      <c r="G31" s="4">
+        <v>2</v>
+      </c>
+      <c r="H31" s="4">
+        <v>9</v>
+      </c>
+      <c r="I31" s="4">
         <v>6</v>
       </c>
-      <c r="F31" s="4">
-        <v>1</v>
-      </c>
-      <c r="G31" s="4">
-        <v>3</v>
-      </c>
-      <c r="H31" s="4">
+      <c r="J31" s="4">
+        <v>1</v>
+      </c>
+      <c r="K31" s="4">
+        <v>3</v>
+      </c>
+      <c r="L31" s="4">
         <v>8028</v>
       </c>
-      <c r="I31" s="5" t="s">
+      <c r="M31" s="5" t="s">
         <v>79</v>
       </c>
     </row>
@@ -2841,7 +3258,7 @@
         <v>萌芽,18,0</v>
       </c>
       <c r="K37" t="str">
-        <f t="shared" ref="K37:O37" si="4">K$35&amp;","&amp;$O4&amp;",0"</f>
+        <f t="shared" ref="K37" si="4">K$35&amp;","&amp;$O4&amp;",0"</f>
         <v>小苗,18,0</v>
       </c>
       <c r="L37" t="str">
@@ -2867,7 +3284,7 @@
     </row>
     <row r="38" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J38" t="str">
-        <f t="shared" ref="J38:N65" si="6">J$35&amp;","&amp;$O5&amp;",0"</f>
+        <f t="shared" ref="J38:K64" si="6">J$35&amp;","&amp;$O5&amp;",0"</f>
         <v>萌芽,18,0</v>
       </c>
       <c r="K38" t="str">
@@ -3351,7 +3768,7 @@
         <v>萌芽,42,0</v>
       </c>
       <c r="K54" t="str">
-        <f t="shared" ref="K54:N54" si="12">K$35&amp;","&amp;$O21&amp;",0"</f>
+        <f t="shared" ref="K54" si="12">K$35&amp;","&amp;$O21&amp;",0"</f>
         <v>小苗,42,0</v>
       </c>
       <c r="L54" t="str">
@@ -3621,7 +4038,7 @@
         <v>萌芽,54,0</v>
       </c>
       <c r="K63" t="str">
-        <f t="shared" ref="K63:N63" si="13">K$35&amp;","&amp;$O30&amp;",0"</f>
+        <f t="shared" ref="K63" si="13">K$35&amp;","&amp;$O30&amp;",0"</f>
         <v>小苗,54,0</v>
       </c>
       <c r="L63" t="str">

--- a/Datas/PlantData.xlsx
+++ b/Datas/PlantData.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory\Rune Factory - Copy\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -242,52 +242,19 @@
     <t>萌芽,24,0|小苗,24,0|大苗,24,2|结果,24,3|成熟,24,3|光杆,0,0</t>
   </si>
   <si>
-    <t>萌芽,36,0|小苗,36,0|大苗,36,1|结果,36,2|成熟,36,2|光杆,12,0</t>
-  </si>
-  <si>
-    <t>萌芽,30,0|小苗,30,0|大苗,30,2|结果,30,3|成熟,30,3|光杆,0,0</t>
-  </si>
-  <si>
-    <t>萌芽,48,0|小苗,48,0|大苗,48,1|结果,48,2|成熟,48,2|光杆,24,0</t>
-  </si>
-  <si>
     <t>萌芽,30,0|小苗,30,0|大苗,30,1|结果,30,2|成熟,30,2|光杆,0,0</t>
   </si>
   <si>
     <t>萌芽,36,0|小苗,36,0|大苗,36,2|结果,36,3|成熟,36,3|光杆,0,0</t>
   </si>
   <si>
-    <t>萌芽,60,0|小苗,60,0|大苗,60,1|结果,60,2|成熟,60,2|光杆,36,0</t>
-  </si>
-  <si>
     <t>萌芽,42,0|小苗,42,0|大苗,42,3|结果,42,4|成熟,42,4|光杆,30,0</t>
   </si>
   <si>
-    <t>萌芽,96,0|小苗,96,0|大苗,96,1|结果,96,2|成熟,96,2|光杆,48,0</t>
-  </si>
-  <si>
     <t>萌芽,36,0|小苗,36,0|大苗,36,1|结果,36,2|成熟,36,2|光杆,0,0</t>
   </si>
   <si>
     <t>萌芽,48,0|小苗,48,0|大苗,48,1|结果,48,2|成熟,48,2|光杆,0,0</t>
-  </si>
-  <si>
-    <t>萌芽,72,0|小苗,72,0|大苗,72,3|结果,72,4|成熟,72,4|光杆,0,0</t>
-  </si>
-  <si>
-    <t>萌芽,72,0|小苗,72,0|大苗,72,2|结果,72,3|成熟,72,3|光杆,0,0</t>
-  </si>
-  <si>
-    <t>萌芽,120,0|小苗,120,0|大苗,120,1|结果,120,2|成熟,120,2|光杆,72,0</t>
-  </si>
-  <si>
-    <t>萌芽,132,0|小苗,132,0|大苗,132,2|结果,132,3|成熟,132,3|光杆,84,0</t>
-  </si>
-  <si>
-    <t>萌芽,120,0|小苗,120,0|大苗,120,3|结果,120,4|成熟,120,4|光杆,72,0</t>
-  </si>
-  <si>
-    <t>萌芽,54,0|小苗,54,0|大苗,54,1|结果,54,2|成熟,54,2|光杆,0,0</t>
   </si>
   <si>
     <t>plantIcon</t>
@@ -315,6 +282,39 @@
   </si>
   <si>
     <t>芜菁_04</t>
+  </si>
+  <si>
+    <t>萌芽,30,0|小苗,30,0|大苗,30,1|结果,30,2|成熟,30,2|光杆,18,0</t>
+  </si>
+  <si>
+    <t>萌芽,36,0|小苗,36,0|大苗,36,1|结果,36,2|成熟,36,2|光杆,36,0</t>
+  </si>
+  <si>
+    <t>萌芽,48,0|小苗,48,0|大苗,48,1|结果,48,2|成熟,48,2|光杆,48,0</t>
+  </si>
+  <si>
+    <t>萌芽,48,0|小苗,48,0|大苗,48,3|结果,48,4|成熟,48,4|光杆,24,0</t>
+  </si>
+  <si>
+    <t>萌芽,60,0|小苗,60,0|大苗,60,1|结果,60,2|成熟,60,2|光杆,84,0</t>
+  </si>
+  <si>
+    <t>萌芽,60,0|小苗,60,0|大苗,60,3|结果,60,4|成熟,60,4|光杆,0,0</t>
+  </si>
+  <si>
+    <t>萌芽,60,0|小苗,60,0|大苗,60,2|结果,60,3|成熟,60,3|光杆,0,0</t>
+  </si>
+  <si>
+    <t>萌芽,96,0|小苗,96,0|大苗,96,1|结果,96,2|成熟,96,2|光杆,96,0</t>
+  </si>
+  <si>
+    <t>萌芽,96,0|小苗,96,0|大苗,96,2|结果,96,3|成熟,96,3|光杆,120,0</t>
+  </si>
+  <si>
+    <t>萌芽,96,0|小苗,96,0|大苗,96,3|结果,96,4|成熟,96,4|光杆,96,0</t>
+  </si>
+  <si>
+    <t>萌芽,72,0|小苗,72,0|大苗,72,1|结果,72,2|成熟,72,2|光杆,72,0</t>
   </si>
 </sst>
 </file>
@@ -734,16 +734,16 @@
         <v>0</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>0</v>
@@ -775,16 +775,16 @@
         <v>5</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>6</v>
@@ -816,7 +816,7 @@
         <v>1001</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F4" s="4">
         <v>1</v>
@@ -831,7 +831,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="4">
         <v>3</v>
@@ -857,7 +857,7 @@
         <v>1002</v>
       </c>
       <c r="E5" s="4" t="str">
-        <f>B5&amp;"_04"</f>
+        <f t="shared" ref="E5:E31" si="0">B5&amp;"_04"</f>
         <v>卷心菜_04</v>
       </c>
       <c r="F5" s="4">
@@ -873,7 +873,7 @@
         <v>3</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="4">
         <v>3</v>
@@ -899,7 +899,7 @@
         <v>1003</v>
       </c>
       <c r="E6" s="4" t="str">
-        <f>B6&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>大葱_04</v>
       </c>
       <c r="F6" s="4">
@@ -915,7 +915,7 @@
         <v>4</v>
       </c>
       <c r="J6" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="4">
         <v>3</v>
@@ -924,7 +924,7 @@
         <v>8003</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.15">
@@ -941,7 +941,7 @@
         <v>1004</v>
       </c>
       <c r="E7" s="4" t="str">
-        <f>B7&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>萝卜_04</v>
       </c>
       <c r="F7" s="4">
@@ -957,7 +957,7 @@
         <v>4</v>
       </c>
       <c r="J7" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="4">
         <v>3</v>
@@ -983,7 +983,7 @@
         <v>1005</v>
       </c>
       <c r="E8" s="4" t="str">
-        <f>B8&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>紫甘蓝_04</v>
       </c>
       <c r="F8" s="4">
@@ -999,7 +999,7 @@
         <v>3</v>
       </c>
       <c r="J8" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="4">
         <v>3</v>
@@ -1025,7 +1025,7 @@
         <v>1006</v>
       </c>
       <c r="E9" s="4" t="str">
-        <f>B9&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>黄瓜_04</v>
       </c>
       <c r="F9" s="4">
@@ -1041,7 +1041,7 @@
         <v>4</v>
       </c>
       <c r="J9" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9" s="4">
         <v>3</v>
@@ -1050,7 +1050,7 @@
         <v>8006</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.15">
@@ -1067,7 +1067,7 @@
         <v>1007</v>
       </c>
       <c r="E10" s="4" t="str">
-        <f>B10&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>西兰花_04</v>
       </c>
       <c r="F10" s="4">
@@ -1083,7 +1083,7 @@
         <v>3</v>
       </c>
       <c r="J10" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="4">
         <v>3</v>
@@ -1092,7 +1092,7 @@
         <v>8007</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.15">
@@ -1109,7 +1109,7 @@
         <v>1008</v>
       </c>
       <c r="E11" s="4" t="str">
-        <f>B11&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>番茄_04</v>
       </c>
       <c r="F11" s="4">
@@ -1125,7 +1125,7 @@
         <v>4</v>
       </c>
       <c r="J11" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" s="4">
         <v>3</v>
@@ -1134,7 +1134,7 @@
         <v>8008</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.15">
@@ -1151,7 +1151,7 @@
         <v>1009</v>
       </c>
       <c r="E12" s="4" t="str">
-        <f>B12&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>胡萝卜_04</v>
       </c>
       <c r="F12" s="4">
@@ -1167,7 +1167,7 @@
         <v>3</v>
       </c>
       <c r="J12" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="4">
         <v>3</v>
@@ -1176,7 +1176,7 @@
         <v>8009</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.15">
@@ -1193,7 +1193,7 @@
         <v>1010</v>
       </c>
       <c r="E13" s="4" t="str">
-        <f>B13&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>西瓜_04</v>
       </c>
       <c r="F13" s="4">
@@ -1209,7 +1209,7 @@
         <v>2</v>
       </c>
       <c r="J13" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="4">
         <v>3</v>
@@ -1218,7 +1218,7 @@
         <v>8010</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.15">
@@ -1235,7 +1235,7 @@
         <v>1011</v>
       </c>
       <c r="E14" s="4" t="str">
-        <f>B14&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>辣椒_04</v>
       </c>
       <c r="F14" s="4">
@@ -1251,7 +1251,7 @@
         <v>5</v>
       </c>
       <c r="J14" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="4">
         <v>3</v>
@@ -1260,7 +1260,7 @@
         <v>8011</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.15">
@@ -1277,7 +1277,7 @@
         <v>1012</v>
       </c>
       <c r="E15" s="4" t="str">
-        <f>B15&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>奇异果_04</v>
       </c>
       <c r="F15" s="4">
@@ -1293,7 +1293,7 @@
         <v>6</v>
       </c>
       <c r="J15" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="4">
         <v>3</v>
@@ -1302,7 +1302,7 @@
         <v>8012</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.15">
@@ -1319,7 +1319,7 @@
         <v>1013</v>
       </c>
       <c r="E16" s="4" t="str">
-        <f>B16&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>茄子_04</v>
       </c>
       <c r="F16" s="4">
@@ -1335,7 +1335,7 @@
         <v>3</v>
       </c>
       <c r="J16" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K16" s="4">
         <v>3</v>
@@ -1344,7 +1344,7 @@
         <v>8013</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.15">
@@ -1361,7 +1361,7 @@
         <v>1014</v>
       </c>
       <c r="E17" s="4" t="str">
-        <f>B17&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>豌豆_04</v>
       </c>
       <c r="F17" s="4">
@@ -1377,7 +1377,7 @@
         <v>6</v>
       </c>
       <c r="J17" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="4">
         <v>3</v>
@@ -1386,7 +1386,7 @@
         <v>8014</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.15">
@@ -1403,7 +1403,7 @@
         <v>1015</v>
       </c>
       <c r="E18" s="4" t="str">
-        <f>B18&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>土豆_04</v>
       </c>
       <c r="F18" s="4">
@@ -1419,7 +1419,7 @@
         <v>4</v>
       </c>
       <c r="J18" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="4">
         <v>3</v>
@@ -1428,7 +1428,7 @@
         <v>8015</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.15">
@@ -1445,7 +1445,7 @@
         <v>1016</v>
       </c>
       <c r="E19" s="4" t="str">
-        <f>B19&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>大蒜_04</v>
       </c>
       <c r="F19" s="4">
@@ -1461,7 +1461,7 @@
         <v>6</v>
       </c>
       <c r="J19" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="4">
         <v>3</v>
@@ -1470,7 +1470,7 @@
         <v>8016</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.15">
@@ -1487,7 +1487,7 @@
         <v>1017</v>
       </c>
       <c r="E20" s="4" t="str">
-        <f>B20&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>芦笋_04</v>
       </c>
       <c r="F20" s="4">
@@ -1502,8 +1502,8 @@
       <c r="I20" s="4">
         <v>4</v>
       </c>
-      <c r="J20" s="4">
-        <v>1</v>
+      <c r="J20" s="6">
+        <v>0</v>
       </c>
       <c r="K20" s="4">
         <v>3</v>
@@ -1512,7 +1512,7 @@
         <v>8017</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.15">
@@ -1529,7 +1529,7 @@
         <v>1018</v>
       </c>
       <c r="E21" s="4" t="str">
-        <f>B21&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>南瓜_04</v>
       </c>
       <c r="F21" s="4">
@@ -1545,7 +1545,7 @@
         <v>3</v>
       </c>
       <c r="J21" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" s="4">
         <v>3</v>
@@ -1554,7 +1554,7 @@
         <v>8018</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.15">
@@ -1571,7 +1571,7 @@
         <v>1019</v>
       </c>
       <c r="E22" s="4" t="str">
-        <f>B22&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>玉米_04</v>
       </c>
       <c r="F22" s="4">
@@ -1587,7 +1587,7 @@
         <v>8</v>
       </c>
       <c r="J22" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="4">
         <v>3</v>
@@ -1596,7 +1596,7 @@
         <v>8019</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.15">
@@ -1613,7 +1613,7 @@
         <v>1020</v>
       </c>
       <c r="E23" s="4" t="str">
-        <f>B23&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>小麦_04</v>
       </c>
       <c r="F23" s="4">
@@ -1629,7 +1629,7 @@
         <v>8</v>
       </c>
       <c r="J23" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="4">
         <v>3</v>
@@ -1638,7 +1638,7 @@
         <v>8020</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.15">
@@ -1655,7 +1655,7 @@
         <v>1021</v>
       </c>
       <c r="E24" s="4" t="str">
-        <f>B24&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>啤酒花_04</v>
       </c>
       <c r="F24" s="4">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="J24" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K24" s="4">
         <v>3</v>
@@ -1680,7 +1680,7 @@
         <v>8021</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.15">
@@ -1697,7 +1697,7 @@
         <v>1022</v>
       </c>
       <c r="E25" s="4" t="str">
-        <f>B25&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>葡萄_04</v>
       </c>
       <c r="F25" s="4">
@@ -1713,7 +1713,7 @@
         <v>8</v>
       </c>
       <c r="J25" s="4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K25" s="4">
         <v>3</v>
@@ -1722,7 +1722,7 @@
         <v>8022</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.15">
@@ -1739,7 +1739,7 @@
         <v>1023</v>
       </c>
       <c r="E26" s="4" t="str">
-        <f>B26&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>菠萝_04</v>
       </c>
       <c r="F26" s="4">
@@ -1755,7 +1755,7 @@
         <v>4</v>
       </c>
       <c r="J26" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K26" s="4">
         <v>3</v>
@@ -1764,7 +1764,7 @@
         <v>8023</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.15">
@@ -1781,7 +1781,7 @@
         <v>1024</v>
       </c>
       <c r="E27" s="4" t="str">
-        <f>B27&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>咖啡_04</v>
       </c>
       <c r="F27" s="4">
@@ -1797,7 +1797,7 @@
         <v>6</v>
       </c>
       <c r="J27" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K27" s="4">
         <v>3</v>
@@ -1806,7 +1806,7 @@
         <v>8024</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.15">
@@ -1823,7 +1823,7 @@
         <v>1025</v>
       </c>
       <c r="E28" s="4" t="str">
-        <f>B28&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>草莓_04</v>
       </c>
       <c r="F28" s="4">
@@ -1839,7 +1839,7 @@
         <v>6</v>
       </c>
       <c r="J28" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K28" s="4">
         <v>3</v>
@@ -1848,7 +1848,7 @@
         <v>8025</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.15">
@@ -1865,7 +1865,7 @@
         <v>1026</v>
       </c>
       <c r="E29" s="4" t="str">
-        <f>B29&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>蓝莓_04</v>
       </c>
       <c r="F29" s="4">
@@ -1881,7 +1881,7 @@
         <v>6</v>
       </c>
       <c r="J29" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K29" s="4">
         <v>3</v>
@@ -1890,7 +1890,7 @@
         <v>8026</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.15">
@@ -1907,7 +1907,7 @@
         <v>1027</v>
       </c>
       <c r="E30" s="4" t="str">
-        <f>B30&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>红薯_04</v>
       </c>
       <c r="F30" s="4">
@@ -1923,7 +1923,7 @@
         <v>6</v>
       </c>
       <c r="J30" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="4">
         <v>3</v>
@@ -1932,7 +1932,7 @@
         <v>8027</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.15">
@@ -1949,7 +1949,7 @@
         <v>1028</v>
       </c>
       <c r="E31" s="4" t="str">
-        <f>B31&amp;"_04"</f>
+        <f t="shared" si="0"/>
         <v>甜菜_04</v>
       </c>
       <c r="F31" s="4">
@@ -1965,7 +1965,7 @@
         <v>6</v>
       </c>
       <c r="J31" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="4">
         <v>3</v>
@@ -1974,7 +1974,7 @@
         <v>8028</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2125,14 +2125,14 @@
         <v>52</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" s="4">
         <v>0</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="M6">
         <f t="shared" si="1"/>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="O6">
         <f t="shared" si="2"/>
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P6">
         <f t="shared" si="3"/>
@@ -2254,14 +2254,14 @@
         <v>52</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K9" s="4">
         <v>2</v>
       </c>
       <c r="L9">
         <f t="shared" si="0"/>
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="M9">
         <f t="shared" si="1"/>
@@ -2269,11 +2269,11 @@
       </c>
       <c r="O9">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="P9">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4">
@@ -2297,14 +2297,14 @@
         <v>52</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10" s="4">
         <v>0</v>
       </c>
       <c r="L10">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="M10">
         <f t="shared" si="1"/>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="O10">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="P10">
         <f t="shared" si="3"/>
@@ -2340,14 +2340,14 @@
         <v>52</v>
       </c>
       <c r="J11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K11" s="4">
         <v>3</v>
       </c>
       <c r="L11">
         <f t="shared" si="0"/>
-        <v>192</v>
+        <v>144</v>
       </c>
       <c r="M11">
         <f t="shared" si="1"/>
@@ -2355,11 +2355,11 @@
       </c>
       <c r="O11">
         <f t="shared" si="2"/>
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="P11">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4">
@@ -2469,14 +2469,14 @@
         <v>52</v>
       </c>
       <c r="J14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K14" s="4">
         <v>4</v>
       </c>
       <c r="L14">
         <f t="shared" si="0"/>
-        <v>240</v>
+        <v>192</v>
       </c>
       <c r="M14">
         <f t="shared" si="1"/>
@@ -2484,11 +2484,11 @@
       </c>
       <c r="O14">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="P14">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4">
@@ -2512,14 +2512,14 @@
         <v>52</v>
       </c>
       <c r="J15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="4">
         <v>3</v>
       </c>
       <c r="L15">
         <f t="shared" si="0"/>
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="M15">
         <f t="shared" si="1"/>
@@ -2527,11 +2527,11 @@
       </c>
       <c r="O15">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P15">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Q15" s="4"/>
       <c r="R15" s="4">
@@ -2555,14 +2555,14 @@
         <v>52</v>
       </c>
       <c r="J16">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K16" s="4">
         <v>6</v>
       </c>
       <c r="L16">
         <f t="shared" si="0"/>
-        <v>384</v>
+        <v>240</v>
       </c>
       <c r="M16">
         <f t="shared" si="1"/>
@@ -2570,11 +2570,11 @@
       </c>
       <c r="O16">
         <f t="shared" si="2"/>
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="P16">
         <f t="shared" si="3"/>
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4">
@@ -2813,14 +2813,14 @@
         <v>52</v>
       </c>
       <c r="J22">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K22" s="4">
         <v>0</v>
       </c>
       <c r="L22">
         <f t="shared" si="0"/>
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="M22">
         <f t="shared" si="1"/>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="O22">
         <f t="shared" si="2"/>
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="P22">
         <f t="shared" si="3"/>
@@ -2856,14 +2856,14 @@
         <v>52</v>
       </c>
       <c r="J23">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K23" s="4">
         <v>0</v>
       </c>
       <c r="L23">
         <f t="shared" si="0"/>
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="M23">
         <f t="shared" si="1"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="O23">
         <f t="shared" si="2"/>
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="P23">
         <f t="shared" si="3"/>
@@ -2899,14 +2899,14 @@
         <v>52</v>
       </c>
       <c r="J24">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K24" s="4">
         <v>8</v>
       </c>
       <c r="L24">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>384</v>
       </c>
       <c r="M24">
         <f t="shared" si="1"/>
@@ -2914,11 +2914,11 @@
       </c>
       <c r="O24">
         <f t="shared" si="2"/>
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="P24">
         <f t="shared" si="3"/>
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="Q24" s="4"/>
       <c r="R24" s="4">
@@ -2942,14 +2942,14 @@
         <v>52</v>
       </c>
       <c r="J25">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K25" s="4">
         <v>9</v>
       </c>
       <c r="L25">
         <f t="shared" si="0"/>
-        <v>528</v>
+        <v>384</v>
       </c>
       <c r="M25">
         <f t="shared" si="1"/>
@@ -2957,11 +2957,11 @@
       </c>
       <c r="O25">
         <f t="shared" si="2"/>
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="P25">
         <f t="shared" si="3"/>
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="Q25" s="4"/>
       <c r="R25" s="4">
@@ -2985,14 +2985,14 @@
         <v>52</v>
       </c>
       <c r="J26">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K26" s="4">
         <v>8</v>
       </c>
       <c r="L26">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>384</v>
       </c>
       <c r="M26">
         <f t="shared" si="1"/>
@@ -3000,11 +3000,11 @@
       </c>
       <c r="O26">
         <f t="shared" si="2"/>
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="P26">
         <f t="shared" si="3"/>
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="Q26" s="4"/>
       <c r="R26" s="4">
@@ -3028,14 +3028,14 @@
         <v>52</v>
       </c>
       <c r="J27">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K27" s="4">
         <v>8</v>
       </c>
       <c r="L27">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>384</v>
       </c>
       <c r="M27">
         <f t="shared" si="1"/>
@@ -3043,11 +3043,11 @@
       </c>
       <c r="O27">
         <f t="shared" si="2"/>
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="P27">
         <f t="shared" si="3"/>
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="Q27" s="4"/>
       <c r="R27" s="4">
@@ -3071,14 +3071,14 @@
         <v>52</v>
       </c>
       <c r="J28">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K28" s="4">
         <v>6</v>
       </c>
       <c r="L28">
         <f t="shared" si="0"/>
-        <v>384</v>
+        <v>288</v>
       </c>
       <c r="M28">
         <f t="shared" si="1"/>
@@ -3086,11 +3086,11 @@
       </c>
       <c r="O28">
         <f t="shared" si="2"/>
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="P28">
         <f t="shared" si="3"/>
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="Q28" s="4"/>
       <c r="R28" s="4">
@@ -3114,14 +3114,14 @@
         <v>52</v>
       </c>
       <c r="J29">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K29" s="4">
         <v>6</v>
       </c>
       <c r="L29">
         <f t="shared" si="0"/>
-        <v>384</v>
+        <v>288</v>
       </c>
       <c r="M29">
         <f t="shared" si="1"/>
@@ -3129,11 +3129,11 @@
       </c>
       <c r="O29">
         <f t="shared" si="2"/>
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="P29">
         <f t="shared" si="3"/>
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="Q29" s="4"/>
       <c r="R29" s="4">
@@ -3157,14 +3157,14 @@
         <v>52</v>
       </c>
       <c r="J30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K30" s="4">
         <v>0</v>
       </c>
       <c r="L30">
         <f t="shared" si="0"/>
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="M30">
         <f t="shared" si="1"/>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O30">
         <f t="shared" si="2"/>
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="P30">
         <f t="shared" si="3"/>
@@ -3200,14 +3200,14 @@
         <v>52</v>
       </c>
       <c r="J31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K31" s="4">
         <v>0</v>
       </c>
       <c r="L31">
         <f t="shared" si="0"/>
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="M31">
         <f t="shared" si="1"/>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="O31">
         <f t="shared" si="2"/>
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="P31">
         <f t="shared" si="3"/>
@@ -3315,23 +3315,23 @@
     <row r="39" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J39" t="str">
         <f t="shared" si="6"/>
-        <v>萌芽,24,0</v>
+        <v>萌芽,18,0</v>
       </c>
       <c r="K39" t="str">
         <f t="shared" si="6"/>
-        <v>小苗,24,0</v>
+        <v>小苗,18,0</v>
       </c>
       <c r="L39" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,24,1</v>
+        <v>大苗,18,1</v>
       </c>
       <c r="M39" t="str">
         <f t="shared" si="8"/>
-        <v>结果,24,2</v>
+        <v>结果,18,2</v>
       </c>
       <c r="N39" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,24,2</v>
+        <v>成熟,18,2</v>
       </c>
       <c r="O39" t="str">
         <f t="shared" si="10"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="Q39" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,24,0|小苗,24,0|大苗,24,1|结果,24,2|成熟,24,2|光杆,0,0</v>
+        <v>萌芽,18,0|小苗,18,0|大苗,18,1|结果,18,2|成熟,18,2|光杆,0,0</v>
       </c>
     </row>
     <row r="40" spans="10:17" x14ac:dyDescent="0.15">
@@ -3405,53 +3405,53 @@
     <row r="42" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J42" t="str">
         <f t="shared" si="6"/>
-        <v>萌芽,36,0</v>
+        <v>萌芽,30,0</v>
       </c>
       <c r="K42" t="str">
         <f t="shared" si="6"/>
-        <v>小苗,36,0</v>
+        <v>小苗,30,0</v>
       </c>
       <c r="L42" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,36,1</v>
+        <v>大苗,30,1</v>
       </c>
       <c r="M42" t="str">
         <f t="shared" si="8"/>
-        <v>结果,36,2</v>
+        <v>结果,30,2</v>
       </c>
       <c r="N42" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,36,2</v>
+        <v>成熟,30,2</v>
       </c>
       <c r="O42" t="str">
         <f t="shared" si="10"/>
-        <v>光杆,12,0</v>
+        <v>光杆,18,0</v>
       </c>
       <c r="Q42" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,36,0|小苗,36,0|大苗,36,1|结果,36,2|成熟,36,2|光杆,12,0</v>
+        <v>萌芽,30,0|小苗,30,0|大苗,30,1|结果,30,2|成熟,30,2|光杆,18,0</v>
       </c>
     </row>
     <row r="43" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J43" t="str">
         <f t="shared" si="6"/>
-        <v>萌芽,30,0</v>
+        <v>萌芽,24,0</v>
       </c>
       <c r="K43" t="str">
         <f t="shared" si="6"/>
-        <v>小苗,30,0</v>
+        <v>小苗,24,0</v>
       </c>
       <c r="L43" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,30,2</v>
+        <v>大苗,24,2</v>
       </c>
       <c r="M43" t="str">
         <f t="shared" si="8"/>
-        <v>结果,30,3</v>
+        <v>结果,24,3</v>
       </c>
       <c r="N43" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,30,3</v>
+        <v>成熟,24,3</v>
       </c>
       <c r="O43" t="str">
         <f t="shared" si="10"/>
@@ -3459,37 +3459,37 @@
       </c>
       <c r="Q43" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,30,0|小苗,30,0|大苗,30,2|结果,30,3|成熟,30,3|光杆,0,0</v>
+        <v>萌芽,24,0|小苗,24,0|大苗,24,2|结果,24,3|成熟,24,3|光杆,0,0</v>
       </c>
     </row>
     <row r="44" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J44" t="str">
         <f t="shared" si="6"/>
-        <v>萌芽,48,0</v>
+        <v>萌芽,36,0</v>
       </c>
       <c r="K44" t="str">
         <f t="shared" si="6"/>
-        <v>小苗,48,0</v>
+        <v>小苗,36,0</v>
       </c>
       <c r="L44" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,48,1</v>
+        <v>大苗,36,1</v>
       </c>
       <c r="M44" t="str">
         <f t="shared" si="8"/>
-        <v>结果,48,2</v>
+        <v>结果,36,2</v>
       </c>
       <c r="N44" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,48,2</v>
+        <v>成熟,36,2</v>
       </c>
       <c r="O44" t="str">
         <f t="shared" si="10"/>
-        <v>光杆,24,0</v>
+        <v>光杆,36,0</v>
       </c>
       <c r="Q44" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,48,0|小苗,48,0|大苗,48,1|结果,48,2|成熟,48,2|光杆,24,0</v>
+        <v>萌芽,36,0|小苗,36,0|大苗,36,1|结果,36,2|成熟,36,2|光杆,36,0</v>
       </c>
     </row>
     <row r="45" spans="10:17" x14ac:dyDescent="0.15">
@@ -3555,91 +3555,91 @@
     <row r="47" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J47" t="str">
         <f t="shared" si="6"/>
-        <v>萌芽,60,0</v>
+        <v>萌芽,48,0</v>
       </c>
       <c r="K47" t="str">
         <f t="shared" si="6"/>
-        <v>小苗,60,0</v>
+        <v>小苗,48,0</v>
       </c>
       <c r="L47" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,60,1</v>
+        <v>大苗,48,1</v>
       </c>
       <c r="M47" t="str">
         <f t="shared" si="8"/>
-        <v>结果,60,2</v>
+        <v>结果,48,2</v>
       </c>
       <c r="N47" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,60,2</v>
+        <v>成熟,48,2</v>
       </c>
       <c r="O47" t="str">
         <f t="shared" si="10"/>
-        <v>光杆,36,0</v>
+        <v>光杆,48,0</v>
       </c>
       <c r="Q47" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,60,0|小苗,60,0|大苗,60,1|结果,60,2|成熟,60,2|光杆,36,0</v>
+        <v>萌芽,48,0|小苗,48,0|大苗,48,1|结果,48,2|成熟,48,2|光杆,48,0</v>
       </c>
     </row>
     <row r="48" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J48" t="str">
         <f t="shared" si="6"/>
-        <v>萌芽,42,0</v>
+        <v>萌芽,48,0</v>
       </c>
       <c r="K48" t="str">
         <f t="shared" si="6"/>
-        <v>小苗,42,0</v>
+        <v>小苗,48,0</v>
       </c>
       <c r="L48" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,42,3</v>
+        <v>大苗,48,3</v>
       </c>
       <c r="M48" t="str">
         <f t="shared" si="8"/>
-        <v>结果,42,4</v>
+        <v>结果,48,4</v>
       </c>
       <c r="N48" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,42,4</v>
+        <v>成熟,48,4</v>
       </c>
       <c r="O48" t="str">
         <f t="shared" si="10"/>
-        <v>光杆,30,0</v>
+        <v>光杆,24,0</v>
       </c>
       <c r="Q48" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,42,0|小苗,42,0|大苗,42,3|结果,42,4|成熟,42,4|光杆,30,0</v>
+        <v>萌芽,48,0|小苗,48,0|大苗,48,3|结果,48,4|成熟,48,4|光杆,24,0</v>
       </c>
     </row>
     <row r="49" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J49" t="str">
         <f t="shared" si="6"/>
-        <v>萌芽,96,0</v>
+        <v>萌芽,60,0</v>
       </c>
       <c r="K49" t="str">
         <f t="shared" si="6"/>
-        <v>小苗,96,0</v>
+        <v>小苗,60,0</v>
       </c>
       <c r="L49" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,96,1</v>
+        <v>大苗,60,1</v>
       </c>
       <c r="M49" t="str">
         <f t="shared" si="8"/>
-        <v>结果,96,2</v>
+        <v>结果,60,2</v>
       </c>
       <c r="N49" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,96,2</v>
+        <v>成熟,60,2</v>
       </c>
       <c r="O49" t="str">
         <f t="shared" si="10"/>
-        <v>光杆,48,0</v>
+        <v>光杆,84,0</v>
       </c>
       <c r="Q49" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,96,0|小苗,96,0|大苗,96,1|结果,96,2|成熟,96,2|光杆,48,0</v>
+        <v>萌芽,60,0|小苗,60,0|大苗,60,1|结果,60,2|成熟,60,2|光杆,84,0</v>
       </c>
     </row>
     <row r="50" spans="10:17" x14ac:dyDescent="0.15">
@@ -3795,23 +3795,23 @@
     <row r="55" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J55" t="str">
         <f t="shared" si="6"/>
-        <v>萌芽,72,0</v>
+        <v>萌芽,60,0</v>
       </c>
       <c r="K55" t="str">
         <f t="shared" si="6"/>
-        <v>小苗,72,0</v>
+        <v>小苗,60,0</v>
       </c>
       <c r="L55" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,72,3</v>
+        <v>大苗,60,3</v>
       </c>
       <c r="M55" t="str">
         <f t="shared" si="8"/>
-        <v>结果,72,4</v>
+        <v>结果,60,4</v>
       </c>
       <c r="N55" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,72,4</v>
+        <v>成熟,60,4</v>
       </c>
       <c r="O55" t="str">
         <f t="shared" si="10"/>
@@ -3819,29 +3819,29 @@
       </c>
       <c r="Q55" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,72,0|小苗,72,0|大苗,72,3|结果,72,4|成熟,72,4|光杆,0,0</v>
+        <v>萌芽,60,0|小苗,60,0|大苗,60,3|结果,60,4|成熟,60,4|光杆,0,0</v>
       </c>
     </row>
     <row r="56" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J56" t="str">
         <f t="shared" si="6"/>
-        <v>萌芽,72,0</v>
+        <v>萌芽,60,0</v>
       </c>
       <c r="K56" t="str">
         <f t="shared" si="6"/>
-        <v>小苗,72,0</v>
+        <v>小苗,60,0</v>
       </c>
       <c r="L56" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,72,2</v>
+        <v>大苗,60,2</v>
       </c>
       <c r="M56" t="str">
         <f t="shared" si="8"/>
-        <v>结果,72,3</v>
+        <v>结果,60,3</v>
       </c>
       <c r="N56" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,72,3</v>
+        <v>成熟,60,3</v>
       </c>
       <c r="O56" t="str">
         <f t="shared" si="10"/>
@@ -3849,209 +3849,209 @@
       </c>
       <c r="Q56" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,72,0|小苗,72,0|大苗,72,2|结果,72,3|成熟,72,3|光杆,0,0</v>
+        <v>萌芽,60,0|小苗,60,0|大苗,60,2|结果,60,3|成熟,60,3|光杆,0,0</v>
       </c>
     </row>
     <row r="57" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J57" t="str">
         <f t="shared" si="6"/>
-        <v>萌芽,120,0</v>
+        <v>萌芽,96,0</v>
       </c>
       <c r="K57" t="str">
         <f t="shared" si="6"/>
-        <v>小苗,120,0</v>
+        <v>小苗,96,0</v>
       </c>
       <c r="L57" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,120,1</v>
+        <v>大苗,96,1</v>
       </c>
       <c r="M57" t="str">
         <f t="shared" si="8"/>
-        <v>结果,120,2</v>
+        <v>结果,96,2</v>
       </c>
       <c r="N57" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,120,2</v>
+        <v>成熟,96,2</v>
       </c>
       <c r="O57" t="str">
         <f t="shared" si="10"/>
-        <v>光杆,72,0</v>
+        <v>光杆,96,0</v>
       </c>
       <c r="Q57" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,120,0|小苗,120,0|大苗,120,1|结果,120,2|成熟,120,2|光杆,72,0</v>
+        <v>萌芽,96,0|小苗,96,0|大苗,96,1|结果,96,2|成熟,96,2|光杆,96,0</v>
       </c>
     </row>
     <row r="58" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J58" t="str">
         <f t="shared" si="6"/>
-        <v>萌芽,132,0</v>
+        <v>萌芽,96,0</v>
       </c>
       <c r="K58" t="str">
         <f t="shared" si="6"/>
-        <v>小苗,132,0</v>
+        <v>小苗,96,0</v>
       </c>
       <c r="L58" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,132,2</v>
+        <v>大苗,96,2</v>
       </c>
       <c r="M58" t="str">
         <f t="shared" si="8"/>
-        <v>结果,132,3</v>
+        <v>结果,96,3</v>
       </c>
       <c r="N58" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,132,3</v>
+        <v>成熟,96,3</v>
       </c>
       <c r="O58" t="str">
         <f t="shared" si="10"/>
-        <v>光杆,84,0</v>
+        <v>光杆,120,0</v>
       </c>
       <c r="Q58" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,132,0|小苗,132,0|大苗,132,2|结果,132,3|成熟,132,3|光杆,84,0</v>
+        <v>萌芽,96,0|小苗,96,0|大苗,96,2|结果,96,3|成熟,96,3|光杆,120,0</v>
       </c>
     </row>
     <row r="59" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J59" t="str">
         <f t="shared" si="6"/>
-        <v>萌芽,120,0</v>
+        <v>萌芽,96,0</v>
       </c>
       <c r="K59" t="str">
         <f t="shared" si="6"/>
-        <v>小苗,120,0</v>
+        <v>小苗,96,0</v>
       </c>
       <c r="L59" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,120,3</v>
+        <v>大苗,96,3</v>
       </c>
       <c r="M59" t="str">
         <f t="shared" si="8"/>
-        <v>结果,120,4</v>
+        <v>结果,96,4</v>
       </c>
       <c r="N59" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,120,4</v>
+        <v>成熟,96,4</v>
       </c>
       <c r="O59" t="str">
         <f t="shared" si="10"/>
-        <v>光杆,72,0</v>
+        <v>光杆,96,0</v>
       </c>
       <c r="Q59" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,120,0|小苗,120,0|大苗,120,3|结果,120,4|成熟,120,4|光杆,72,0</v>
+        <v>萌芽,96,0|小苗,96,0|大苗,96,3|结果,96,4|成熟,96,4|光杆,96,0</v>
       </c>
     </row>
     <row r="60" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J60" t="str">
         <f t="shared" si="6"/>
-        <v>萌芽,120,0</v>
+        <v>萌芽,96,0</v>
       </c>
       <c r="K60" t="str">
         <f t="shared" si="6"/>
-        <v>小苗,120,0</v>
+        <v>小苗,96,0</v>
       </c>
       <c r="L60" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,120,1</v>
+        <v>大苗,96,1</v>
       </c>
       <c r="M60" t="str">
         <f t="shared" si="8"/>
-        <v>结果,120,2</v>
+        <v>结果,96,2</v>
       </c>
       <c r="N60" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,120,2</v>
+        <v>成熟,96,2</v>
       </c>
       <c r="O60" t="str">
         <f t="shared" si="10"/>
-        <v>光杆,72,0</v>
+        <v>光杆,96,0</v>
       </c>
       <c r="Q60" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,120,0|小苗,120,0|大苗,120,1|结果,120,2|成熟,120,2|光杆,72,0</v>
+        <v>萌芽,96,0|小苗,96,0|大苗,96,1|结果,96,2|成熟,96,2|光杆,96,0</v>
       </c>
     </row>
     <row r="61" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J61" t="str">
         <f t="shared" si="6"/>
-        <v>萌芽,96,0</v>
+        <v>萌芽,72,0</v>
       </c>
       <c r="K61" t="str">
         <f t="shared" si="6"/>
-        <v>小苗,96,0</v>
+        <v>小苗,72,0</v>
       </c>
       <c r="L61" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,96,1</v>
+        <v>大苗,72,1</v>
       </c>
       <c r="M61" t="str">
         <f t="shared" si="8"/>
-        <v>结果,96,2</v>
+        <v>结果,72,2</v>
       </c>
       <c r="N61" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,96,2</v>
+        <v>成熟,72,2</v>
       </c>
       <c r="O61" t="str">
         <f t="shared" si="10"/>
-        <v>光杆,48,0</v>
+        <v>光杆,72,0</v>
       </c>
       <c r="Q61" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,96,0|小苗,96,0|大苗,96,1|结果,96,2|成熟,96,2|光杆,48,0</v>
+        <v>萌芽,72,0|小苗,72,0|大苗,72,1|结果,72,2|成熟,72,2|光杆,72,0</v>
       </c>
     </row>
     <row r="62" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J62" t="str">
         <f t="shared" si="6"/>
-        <v>萌芽,96,0</v>
+        <v>萌芽,72,0</v>
       </c>
       <c r="K62" t="str">
         <f t="shared" si="6"/>
-        <v>小苗,96,0</v>
+        <v>小苗,72,0</v>
       </c>
       <c r="L62" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,96,1</v>
+        <v>大苗,72,1</v>
       </c>
       <c r="M62" t="str">
         <f t="shared" si="8"/>
-        <v>结果,96,2</v>
+        <v>结果,72,2</v>
       </c>
       <c r="N62" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,96,2</v>
+        <v>成熟,72,2</v>
       </c>
       <c r="O62" t="str">
         <f t="shared" si="10"/>
-        <v>光杆,48,0</v>
+        <v>光杆,72,0</v>
       </c>
       <c r="Q62" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,96,0|小苗,96,0|大苗,96,1|结果,96,2|成熟,96,2|光杆,48,0</v>
+        <v>萌芽,72,0|小苗,72,0|大苗,72,1|结果,72,2|成熟,72,2|光杆,72,0</v>
       </c>
     </row>
     <row r="63" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J63" t="str">
         <f>J$35&amp;","&amp;$O30&amp;",0"</f>
-        <v>萌芽,54,0</v>
+        <v>萌芽,48,0</v>
       </c>
       <c r="K63" t="str">
         <f t="shared" ref="K63" si="13">K$35&amp;","&amp;$O30&amp;",0"</f>
-        <v>小苗,54,0</v>
+        <v>小苗,48,0</v>
       </c>
       <c r="L63" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,54,1</v>
+        <v>大苗,48,1</v>
       </c>
       <c r="M63" t="str">
         <f t="shared" si="8"/>
-        <v>结果,54,2</v>
+        <v>结果,48,2</v>
       </c>
       <c r="N63" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,54,2</v>
+        <v>成熟,48,2</v>
       </c>
       <c r="O63" t="str">
         <f t="shared" si="10"/>
@@ -4059,29 +4059,29 @@
       </c>
       <c r="Q63" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,54,0|小苗,54,0|大苗,54,1|结果,54,2|成熟,54,2|光杆,0,0</v>
+        <v>萌芽,48,0|小苗,48,0|大苗,48,1|结果,48,2|成熟,48,2|光杆,0,0</v>
       </c>
     </row>
     <row r="64" spans="10:17" x14ac:dyDescent="0.15">
       <c r="J64" t="str">
         <f t="shared" si="6"/>
-        <v>萌芽,54,0</v>
+        <v>萌芽,48,0</v>
       </c>
       <c r="K64" t="str">
         <f t="shared" si="6"/>
-        <v>小苗,54,0</v>
+        <v>小苗,48,0</v>
       </c>
       <c r="L64" t="str">
         <f t="shared" si="7"/>
-        <v>大苗,54,1</v>
+        <v>大苗,48,1</v>
       </c>
       <c r="M64" t="str">
         <f t="shared" si="8"/>
-        <v>结果,54,2</v>
+        <v>结果,48,2</v>
       </c>
       <c r="N64" t="str">
         <f t="shared" si="9"/>
-        <v>成熟,54,2</v>
+        <v>成熟,48,2</v>
       </c>
       <c r="O64" t="str">
         <f t="shared" si="10"/>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="Q64" t="str">
         <f t="shared" si="11"/>
-        <v>萌芽,54,0|小苗,54,0|大苗,54,1|结果,54,2|成熟,54,2|光杆,0,0</v>
+        <v>萌芽,48,0|小苗,48,0|大苗,48,1|结果,48,2|成熟,48,2|光杆,0,0</v>
       </c>
     </row>
   </sheetData>
